--- a/family_asset_records.xlsx
+++ b/family_asset_records.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2709,6 +2709,67 @@
       </c>
       <c r="S37" t="n">
         <v>1079037</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3707280</v>
+      </c>
+      <c r="C38" t="n">
+        <v>33453</v>
+      </c>
+      <c r="D38" t="n">
+        <v>74355</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3824082</v>
+      </c>
+      <c r="F38" t="n">
+        <v>7787</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>10229255</v>
+      </c>
+      <c r="I38" t="n">
+        <v>15730</v>
+      </c>
+      <c r="J38" t="n">
+        <v>19561</v>
+      </c>
+      <c r="K38" t="n">
+        <v>10016503</v>
+      </c>
+      <c r="L38" t="n">
+        <v>20687</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3815088</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3831869</v>
+      </c>
+      <c r="P38" t="n">
+        <v>10264546</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>10037190</v>
+      </c>
+      <c r="R38" t="n">
+        <v>27948693</v>
+      </c>
+      <c r="S38" t="n">
+        <v>-1894323</v>
       </c>
     </row>
   </sheetData>
@@ -2722,7 +2783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2746,6 +2807,11 @@
           <t>月增減</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>月成長率</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2762,6 +2828,9 @@
       <c r="D2" t="n">
         <v>6218939</v>
       </c>
+      <c r="E2" t="n">
+        <v>28.63</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2773,10 +2842,13 @@
         <v>28233867</v>
       </c>
       <c r="C3" t="n">
-        <v>29843016</v>
+        <v>27948693</v>
       </c>
       <c r="D3" t="n">
-        <v>1609149</v>
+        <v>-285174</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.01</v>
       </c>
     </row>
   </sheetData>
@@ -2790,7 +2862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2814,6 +2886,11 @@
           <t>年增減</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>年成長率</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2825,10 +2902,13 @@
         <v>21718841</v>
       </c>
       <c r="C2" t="n">
-        <v>29843016</v>
+        <v>27948693</v>
       </c>
       <c r="D2" t="n">
-        <v>8124175</v>
+        <v>6229852</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.68</v>
       </c>
     </row>
   </sheetData>
